--- a/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,64; 31,66</t>
+          <t>22,6; 31,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,43; 22,46</t>
+          <t>13,52; 22,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,43</t>
+          <t>1,63; 10,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,94; 23,47</t>
+          <t>15,74; 23,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 19,03</t>
+          <t>10,77; 18,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 14,41</t>
+          <t>6,92; 14,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,46; 25,93</t>
+          <t>19,88; 25,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 19,12</t>
+          <t>13,26; 19,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 12,05</t>
+          <t>6,33; 11,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>99,86; 172,86</t>
+          <t>102,86; 170,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,89; 122,89</t>
+          <t>60,86; 122,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 56,9</t>
+          <t>6,94; 54,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56,83; 97,15</t>
+          <t>56,43; 98,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,84; 78,08</t>
+          <t>38,49; 76,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 59,62</t>
+          <t>24,94; 59,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,3; 115,87</t>
+          <t>78,88; 115,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,08; 85,31</t>
+          <t>52,66; 85,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,57; 53,49</t>
+          <t>24,9; 52,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,57; 35,85</t>
+          <t>29,09; 35,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,81; 22,94</t>
+          <t>16,03; 23,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,19</t>
+          <t>-2,81; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,52; 37,82</t>
+          <t>31,09; 38,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,11; 27,19</t>
+          <t>19,8; 26,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 27,71</t>
+          <t>-3,84; 30,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,99; 36,16</t>
+          <t>30,79; 35,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,14; 24,13</t>
+          <t>18,99; 24,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 20,0</t>
+          <t>-1,94; 19,36</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>118,19; 178,64</t>
+          <t>120,0; 177,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,27; 114,15</t>
+          <t>66,36; 112,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 20,51</t>
+          <t>-12,05; 19,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111,02; 159,61</t>
+          <t>108,64; 159,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,34; 115,13</t>
+          <t>70,39; 112,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 112,48</t>
+          <t>-14,47; 120,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>122,0; 161,11</t>
+          <t>120,88; 158,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,32; 107,83</t>
+          <t>75,05; 108,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 86,74</t>
+          <t>-7,96; 83,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,04; 33,68</t>
+          <t>18,7; 33,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,37; 31,06</t>
+          <t>15,46; 30,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 2,05</t>
+          <t>-10,58; 1,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,92; 35,79</t>
+          <t>21,08; 35,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,61; 30,45</t>
+          <t>16,56; 29,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -2,09</t>
+          <t>-14,16; -2,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,07; 32,31</t>
+          <t>22,29; 32,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,43; 28,33</t>
+          <t>18,58; 29,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -1,65</t>
+          <t>-10,51; -1,96</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67,98; 163,06</t>
+          <t>65,75; 154,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57,3; 146,88</t>
+          <t>55,04; 140,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 10,06</t>
+          <t>-37,11; 7,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,76; 147,61</t>
+          <t>67,89; 147,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,84; 129,34</t>
+          <t>53,14; 122,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,16; -8,43</t>
+          <t>-45,09; -10,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,59; 137,45</t>
+          <t>77,04; 138,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,93; 119,64</t>
+          <t>65,48; 124,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,37; -6,99</t>
+          <t>-36,32; -8,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,49; 32,62</t>
+          <t>27,18; 32,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,22; 22,31</t>
+          <t>17,11; 22,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,53</t>
+          <t>-1,5; 3,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,46; 30,33</t>
+          <t>25,57; 30,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,19; 23,4</t>
+          <t>18,23; 23,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 23,25</t>
+          <t>-0,81; 22,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,03; 30,66</t>
+          <t>27,1; 30,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,65; 22,27</t>
+          <t>18,3; 22,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 16,57</t>
+          <t>-0,23; 13,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>120,28; 160,45</t>
+          <t>117,88; 158,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74,32; 108,9</t>
+          <t>73,97; 110,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 17,17</t>
+          <t>-6,62; 16,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92,26; 122,04</t>
+          <t>92,86; 121,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>66,78; 93,48</t>
+          <t>65,93; 92,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 90,57</t>
+          <t>-2,78; 88,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>107,99; 131,57</t>
+          <t>107,08; 131,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74,54; 95,6</t>
+          <t>73,09; 94,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 68,66</t>
+          <t>-0,94; 55,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>11,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,0</t>
+          <t>9,32</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,6; 31,12</t>
+          <t>22,2; 31,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 22,53</t>
+          <t>13,43; 22,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,23</t>
+          <t>1,11; 9,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,74; 23,62</t>
+          <t>16,2; 23,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 18,83</t>
+          <t>10,3; 18,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,46</t>
+          <t>7,96; 15,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,88; 25,86</t>
+          <t>20,22; 25,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 19,36</t>
+          <t>12,97; 19,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 11,89</t>
+          <t>6,53; 11,99</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>102,86; 170,25</t>
+          <t>99,93; 168,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,86; 122,56</t>
+          <t>59,06; 119,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 54,26</t>
+          <t>5,38; 54,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56,43; 98,16</t>
+          <t>56,85; 97,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,49; 76,94</t>
+          <t>36,62; 76,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,94; 59,34</t>
+          <t>27,88; 61,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,88; 115,94</t>
+          <t>80,61; 116,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,66; 85,94</t>
+          <t>52,17; 86,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,9; 52,59</t>
+          <t>26,51; 53,93</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>1,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,09; 35,63</t>
+          <t>28,94; 35,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 23,12</t>
+          <t>16,09; 23,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,99</t>
+          <t>-0,98; 5,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,09; 38,44</t>
+          <t>31,12; 38,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,8; 26,89</t>
+          <t>20,16; 27,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 30,32</t>
+          <t>-3,59; 3,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,79; 35,8</t>
+          <t>30,78; 35,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,99; 24,32</t>
+          <t>19,23; 24,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 19,36</t>
+          <t>-1,37; 3,36</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>-0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>120,0; 177,89</t>
+          <t>121,34; 180,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,36; 112,71</t>
+          <t>67,44; 115,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 19,22</t>
+          <t>-3,63; 30,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108,64; 159,62</t>
+          <t>111,65; 159,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,39; 112,89</t>
+          <t>71,57; 113,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 120,58</t>
+          <t>-13,08; 12,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>120,88; 158,16</t>
+          <t>121,33; 159,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,05; 108,1</t>
+          <t>75,59; 105,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 83,29</t>
+          <t>-5,57; 14,49</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,33</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,75</t>
+          <t>-7,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,04</t>
+          <t>-5,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,7; 33,52</t>
+          <t>19,27; 33,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,46; 30,71</t>
+          <t>16,27; 30,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 1,47</t>
+          <t>-9,53; 2,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,08; 35,63</t>
+          <t>20,93; 35,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 29,86</t>
+          <t>16,24; 30,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -2,45</t>
+          <t>-13,02; -1,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,29; 32,72</t>
+          <t>22,14; 32,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,58; 29,03</t>
+          <t>18,78; 28,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -1,96</t>
+          <t>-9,37; -1,34</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-17,57%</t>
+          <t>-14,28%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,97%</t>
+          <t>-26,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-23,08%</t>
+          <t>-20,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,75; 154,52</t>
+          <t>67,78; 157,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,04; 140,73</t>
+          <t>58,59; 146,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 7,34</t>
+          <t>-34,6; 13,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67,89; 147,71</t>
+          <t>64,88; 144,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,14; 122,65</t>
+          <t>51,96; 125,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,09; -10,09</t>
+          <t>-41,04; -6,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,04; 138,27</t>
+          <t>75,68; 138,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,48; 124,57</t>
+          <t>64,52; 119,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,32; -8,22</t>
+          <t>-33,05; -5,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,18; 32,42</t>
+          <t>27,29; 32,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,11; 22,46</t>
+          <t>17,08; 22,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,55</t>
+          <t>-0,21; 4,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,57; 30,44</t>
+          <t>25,31; 30,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,23; 23,19</t>
+          <t>18,18; 23,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 22,36</t>
+          <t>-0,39; 3,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,1; 30,54</t>
+          <t>26,97; 30,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,3; 22,11</t>
+          <t>18,45; 22,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 13,64</t>
+          <t>0,35; 3,6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>117,88; 158,29</t>
+          <t>118,2; 157,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,97; 110,14</t>
+          <t>74,39; 110,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 16,98</t>
+          <t>-0,99; 23,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92,86; 121,68</t>
+          <t>93,07; 122,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>65,93; 92,53</t>
+          <t>66,06; 92,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 88,06</t>
+          <t>-1,45; 15,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>107,08; 131,28</t>
+          <t>106,65; 130,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>73,09; 94,66</t>
+          <t>72,88; 94,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 55,82</t>
+          <t>1,4; 15,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
